--- a/docs/菜单.xlsx
+++ b/docs/菜单.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\family-ledger_RevB\Lunch_HP\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A486E0C7-B506-4EE8-B9F2-6DBEF5C2F822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B2C3902-4009-422E-9E9E-9ADDE522A124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="name list" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="56">
   <si>
     <t>No</t>
   </si>
@@ -194,141 +193,6 @@
   </si>
   <si>
     <t>豪華三拼牛肉雞胸蝦仁烤蔬套餐</t>
-  </si>
-  <si>
-    <t>Name List</t>
-  </si>
-  <si>
-    <t>Dou, Cindy</t>
-  </si>
-  <si>
-    <t>Ge, Neal</t>
-  </si>
-  <si>
-    <t>Guo, Xiao-Jian</t>
-  </si>
-  <si>
-    <t>Hu, Yao-Qing</t>
-  </si>
-  <si>
-    <t>Liu, Jianping</t>
-  </si>
-  <si>
-    <t>Mao, Kun</t>
-  </si>
-  <si>
-    <t>Qiao, Xiu-Jun</t>
-  </si>
-  <si>
-    <t>Shi, Zhao-Yong</t>
-  </si>
-  <si>
-    <t>Su, Jun</t>
-  </si>
-  <si>
-    <t>Wan, Jia-Nian</t>
-  </si>
-  <si>
-    <t>Wang, Cheng-Yu</t>
-  </si>
-  <si>
-    <t>Xiong, Wenjun</t>
-  </si>
-  <si>
-    <t>Xu, Jian</t>
-  </si>
-  <si>
-    <t>Yan, Hong-Ming</t>
-  </si>
-  <si>
-    <t>Zeng, Daniel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zhang, Hai-Tao </t>
-  </si>
-  <si>
-    <t>Zhang, Xin-Guo</t>
-  </si>
-  <si>
-    <t>Zhou, HongLiang</t>
-  </si>
-  <si>
-    <t>Zhou Yong</t>
-  </si>
-  <si>
-    <t>Alex</t>
-  </si>
-  <si>
-    <t>Tang, hong</t>
-  </si>
-  <si>
-    <t>Tua, Marta</t>
-  </si>
-  <si>
-    <t>Javier Velazquez</t>
-  </si>
-  <si>
-    <t>Anna</t>
-  </si>
-  <si>
-    <t>JORDI MUNCUNILL FARRES</t>
-  </si>
-  <si>
-    <t>ALEJANDRO ALARCON CANO</t>
-  </si>
-  <si>
-    <t>Li Peng zhen</t>
-  </si>
-  <si>
-    <t>Pau Serra</t>
-  </si>
-  <si>
-    <t>Sheila Cabello</t>
-  </si>
-  <si>
-    <t>Miquel Riera</t>
-  </si>
-  <si>
-    <t>Chuah, Nee Heng</t>
-  </si>
-  <si>
-    <t>Juan Esteban Rangel</t>
-  </si>
-  <si>
-    <t>Raquel Wamp</t>
-  </si>
-  <si>
-    <t>Gabriel Nogales</t>
-  </si>
-  <si>
-    <t>Guille Erraez,</t>
-  </si>
-  <si>
-    <t>Miquel Riera,</t>
-  </si>
-  <si>
-    <t>Ignacio Alejandre,</t>
-  </si>
-  <si>
-    <t>Claudia Peiró</t>
-  </si>
-  <si>
-    <t>Victor Serra</t>
-  </si>
-  <si>
-    <t>Roger</t>
-  </si>
-  <si>
-    <t>Alberto</t>
-  </si>
-  <si>
-    <t>Alvin</t>
-  </si>
-  <si>
-    <t>Huang Tao</t>
-  </si>
-  <si>
-    <t>Teo Kian Chai</t>
   </si>
 </sst>
 </file>
@@ -1405,242 +1269,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB2FADDD-EB6A-431E-9A01-075AAC40347D}">
-  <dimension ref="A1:A45"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="24.7265625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>